--- a/05_Figures/F06_prediction/proteins/training/d_fcsa_I/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/training/d_fcsa_I/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="206">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -128,34 +128,49 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
+    <t xml:space="preserve">TUBB2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GATD3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL22</t>
+  </si>
+  <si>
     <t xml:space="preserve">STK38</t>
   </si>
   <si>
-    <t xml:space="preserve">CBR4</t>
+    <t xml:space="preserve">TMEM205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRIP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF5B</t>
   </si>
   <si>
     <t xml:space="preserve">ERGIC1</t>
   </si>
   <si>
-    <t xml:space="preserve">GATD3B</t>
+    <t xml:space="preserve">FSCN1</t>
   </si>
   <si>
     <t xml:space="preserve">GLRX5</t>
   </si>
   <si>
+    <t xml:space="preserve">MFN2</t>
+  </si>
+  <si>
     <t xml:space="preserve">NDUFS4</t>
   </si>
   <si>
-    <t xml:space="preserve">TMEM205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBB2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL22</t>
+    <t xml:space="preserve">OGDH</t>
   </si>
   <si>
     <t xml:space="preserve">PGAM1</t>
@@ -167,568 +182,454 @@
     <t xml:space="preserve">ACTR1A</t>
   </si>
   <si>
+    <t xml:space="preserve">ATP5F1E</t>
+  </si>
+  <si>
     <t xml:space="preserve">CD36</t>
   </si>
   <si>
-    <t xml:space="preserve">EIF5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FSCN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MFN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OGDH</t>
+    <t xml:space="preserve">NDUFB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSAPL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UFD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYPLA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP3K20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHKA1</t>
   </si>
   <si>
     <t xml:space="preserve">RPL17</t>
   </si>
   <si>
-    <t xml:space="preserve">RTN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRIP2</t>
+    <t xml:space="preserve">RYR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASPH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB11B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSFM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CKMT1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SFPQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GFM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSD17B4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDLIM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC23A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2B</t>
   </si>
   <si>
     <t xml:space="preserve">DDAH2</t>
   </si>
   <si>
-    <t xml:space="preserve">LYPLA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSAPL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UFD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASPH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPB8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RYR1</t>
+    <t xml:space="preserve">DPYSL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GGCT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDIA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLGRKT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QDPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNX5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STK38L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACAA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACSS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOBEC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATAD3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDNF</t>
   </si>
   <si>
     <t xml:space="preserve">CHMP2A</t>
   </si>
   <si>
-    <t xml:space="preserve">CUL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP3K20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHKA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB11B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSFM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5F1E</t>
+    <t xml:space="preserve">CHMP6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLOD4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPS27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MTARC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHKG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRUNE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SETD7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3BGRL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPCS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACYP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKR1C1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANP32A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARF6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARHGDIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP2A3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLIP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX6B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX7A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPNE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSDE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DECR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPTOR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1LI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHD4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FHOD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRHPR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDHD5</t>
   </si>
   <si>
     <t xml:space="preserve">HECTD1</t>
   </si>
   <si>
-    <t xml:space="preserve">NDUFB5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GFM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDIA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC23A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">APOBEC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CKMT1A</t>
-  </si>
-  <si>
     <t xml:space="preserve">HNRNPA3</t>
   </si>
   <si>
-    <t xml:space="preserve">HSD17B4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDLIM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLGRKT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNX5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPYSL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLOD4</t>
+    <t xml:space="preserve">HNRNPK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPCAL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB6</t>
   </si>
   <si>
     <t xml:space="preserve">IFITM1</t>
   </si>
   <si>
-    <t xml:space="preserve">SH3BGRL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGDIB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDNF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EHD4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GGCT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDHD5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDH2</t>
+    <t xml:space="preserve">LDHB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYPLA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP1LC3B2</t>
   </si>
   <si>
     <t xml:space="preserve">MAPRE1</t>
   </si>
   <si>
-    <t xml:space="preserve">MTARC2</t>
+    <t xml:space="preserve">MAPRE2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPRE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MECR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGST2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MLIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYH9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYO1C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAGK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAXE</t>
   </si>
   <si>
     <t xml:space="preserve">NDUFB9</t>
   </si>
   <si>
+    <t xml:space="preserve">NGLY1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFDN4</t>
+  </si>
+  <si>
     <t xml:space="preserve">PFKM</t>
   </si>
   <si>
-    <t xml:space="preserve">PHKG1</t>
+    <t xml:space="preserve">PGP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PHKB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRDX3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKAA2</t>
   </si>
   <si>
     <t xml:space="preserve">PRKCSH</t>
   </si>
   <si>
-    <t xml:space="preserve">PRUNE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QDPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUVBL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SFPQ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SMIM4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STK38L</t>
+    <t xml:space="preserve">PSMA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RBBP4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RHOA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL27A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RYR2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC31A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGCD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHMT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNX3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNJ2BP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TACC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPM4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSPO</t>
   </si>
   <si>
     <t xml:space="preserve">TXN2</t>
   </si>
   <si>
+    <t xml:space="preserve">UBA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UQCRC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WARS1</t>
+  </si>
+  <si>
     <t xml:space="preserve">XRCC5</t>
   </si>
   <si>
-    <t xml:space="preserve">ACAA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACTR1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACYP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKR1C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANP32A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATAD3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP2A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CISD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLIP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX6B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX7A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPNE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSDE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DBT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DECR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DEPTOR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS7B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1LI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EPRS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FHOD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FYCO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRHPR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTM4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-DRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPCAL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPB6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LDHB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMAN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LUM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LYPLA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP1LC3B2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP2K2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MARCKS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MECR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGST2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MLIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MOB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYH9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYO1C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAGK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NAXE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFS8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NGLY1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUDC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PABPC4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PCCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFDN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHKB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRDX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKAA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSMD6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB8A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RBBP4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL27A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS4X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RYR2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC31A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SETD7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGCD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3BGRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SHMT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SNX3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPCS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPPL2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STT3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STT3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYNCRIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYNJ2BP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TACC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPM4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSPO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UBA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UQCRC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VDAC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WARS1</t>
-  </si>
-  <si>
     <t xml:space="preserve">YARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YWHAQ</t>
   </si>
   <si>
     <t xml:space="preserve">ZYX</t>
@@ -1118,16 +1019,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.83408859443086</v>
+        <v>-1.96453122277527</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.793406593406593</v>
+        <v>-0.846153846153846</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1151,29 +1052,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.83408859443086</v>
+        <v>-1.96453122277527</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.793406593406593</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.930348258706468</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.995024875621891</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.681451811950276</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.748062998361208</v>
-      </c>
+        <v>-0.846153846153846</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1197,2206 +1090,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1.67605620246171</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-1.08921180429414</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-3.13379787888361</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.792633451956151</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.110778721869905</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.293899522468258</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.379121268155564</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-2.08446745615039</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.651912185823805</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.2899072864398</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.0693749508980384</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.255663623985139</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.67759165989942</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.497282223663011</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.16134057546192</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-1.09609482372093</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.53761957696334</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-2.06901833630132</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-1.0094720675161</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.16502547376757</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-2.03627011202441</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-0.93066987367655</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-1.61819154895743</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.195174846932149</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.113557058503783</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.905414488955733</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.059516884069424</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.447375455059937</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-1.41054708686555</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-0.991274426534442</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-1.04923520687194</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.038805307121117</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.0415276291185178</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.59762791003207</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.315120523164082</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.37533257268141</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-1.39695518129637</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.396744861162561</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.354786269578366</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.20299747620573</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.34616041244235</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-2.30006467469464</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.969950525660057</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.0873222690054987</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.0505276294564543</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.434937583852952</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.264103705668975</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.269102894420644</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.670754473923625</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.121639192401644</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.229048541995558</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-2.39837637757258</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-1.56194925586615</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.604605655125912</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-0.739367255412894</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.959716518771317</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.383931117873218</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-1.47937419783217</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.680068133588937</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.000451741051758825</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.942505811533965</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.195980557783769</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.379323028752724</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>0.137322548368478</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0.3228870733233</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.468120510891865</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.64949873273194</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-1.30608479814966</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-1.18697456452264</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-0.611889843049894</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.901023811001804</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-1.11481644876516</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-1.5696214236041</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-3.1662964510938</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-0.848520002193802</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>-0.540252732157249</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.503585358824396</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.0791368507257231</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.745352480722158</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>0.670818626708742</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-1.63990319831305</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0.00616751781417391</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0.756031982307786</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-3.06356016632214</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.782085881360362</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-0.983198436693405</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-1.54800519443494</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>0.101285448675929</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.532037701104176</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-3.03287888162562</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.358129845463644</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-1.90632530430299</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-0.256141468072239</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0.100224546560986</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-1.74367527256005</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.567722115663955</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.395719357719699</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.593484190497685</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-0.467385681718478</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.165921640652458</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.663047393948335</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-2.70619353459381</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-1.52299101740565</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.513994903799215</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.972761108455676</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.839512436531504</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-1.51910683328156</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.0377478576408046</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.173248024193853</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.940832697056525</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-0.0449742622173241</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>0.0502656196995174</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>0.425917419408088</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>0.016042936533265</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-1.18047136979163</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.60806813709984</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.779998184164355</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-2.46972453826847</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-1.14613781101192</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.681956499211487</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.372936104497365</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.851122723619264</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.252066816612305</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.666887592777632</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.590333250695522</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.0420789186512569</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.406496577115725</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-1.76060680573605</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-1.08540351230914</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-1.42711763795936</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.307842089789101</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.257708838589522</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.670333787288003</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.200973417431278</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.442977723313595</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.223051428212491</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-0.493795795437514</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.689439906348976</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.0881647335048032</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>0.132710250475872</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>0.0592995944292891</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>0.206378376714976</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-1.32238545313133</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.550628782644448</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>0.140168716702463</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.563786501939719</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.440955895047345</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.185347877228816</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.204570358392608</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>0.312022248763968</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.545715086220025</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.0539792746855137</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-1.37640613888969</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.44228578591892</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-1.1033249882508</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.566464154692494</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>0.449515542409009</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.804474193074428</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-2.17881564016822</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.480071808024382</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-1.48976988216157</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-0.874543707518323</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.454529347555263</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>0.0099162572444601</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-1.79484203783989</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.944325964663946</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.265427885979419</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-1.11728468210611</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.678067044449771</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.138365799480596</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>0.0521729540979581</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>0.110520970777945</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>0.480985383063968</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>-0.16691583348076</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>0.0713836388091562</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.129001329034757</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>0.530766814100055</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.564353868085499</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0.234301341988809</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.195692569320656</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.0445163808082438</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-0.0898009145712133</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-2.38865798536738</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0.119071338658819</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.602219856265247</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.807356740105031</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-0.664852348936668</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0.146439076989252</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.611371457364481</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-0.679805309799877</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.0742193556175752</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-1.02846935487763</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-1.34547325392038</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.839103531408738</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.431243358931564</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.757311838719891</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-1.08362013453374</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-1.80286621305147</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-1.51001010924705</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-0.98874542920237</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3439,7 +1132,7 @@
         <v>874.31</v>
       </c>
       <c r="E2" t="n">
-        <v>-2024.04416965673</v>
+        <v>-2053.49130712163</v>
       </c>
     </row>
     <row r="3">
@@ -3456,7 +1149,7 @@
         <v>1757.71</v>
       </c>
       <c r="E3" t="n">
-        <v>-1183.95376649092</v>
+        <v>-1129.78145418981</v>
       </c>
     </row>
     <row r="4">
@@ -3473,7 +1166,7 @@
         <v>1924.77</v>
       </c>
       <c r="E4" t="n">
-        <v>-1736.44758473943</v>
+        <v>-1452.54324649965</v>
       </c>
     </row>
     <row r="5">
@@ -3490,7 +1183,7 @@
         <v>274.62</v>
       </c>
       <c r="E5" t="n">
-        <v>574.666500039495</v>
+        <v>524.843379065547</v>
       </c>
     </row>
     <row r="6">
@@ -3507,7 +1200,7 @@
         <v>545.54</v>
       </c>
       <c r="E6" t="n">
-        <v>-5.07919697467054</v>
+        <v>-96.9900809172358</v>
       </c>
     </row>
     <row r="7">
@@ -3524,7 +1217,7 @@
         <v>1276.8</v>
       </c>
       <c r="E7" t="n">
-        <v>-2789.80360483498</v>
+        <v>-2741.16117712546</v>
       </c>
     </row>
     <row r="8">
@@ -3541,7 +1234,7 @@
         <v>171.549999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>342.84889847771</v>
+        <v>418.73079881828</v>
       </c>
     </row>
     <row r="9">
@@ -3558,7 +1251,7 @@
         <v>621.64</v>
       </c>
       <c r="E9" t="n">
-        <v>-250.519120012645</v>
+        <v>-157.950996362466</v>
       </c>
     </row>
     <row r="10">
@@ -3575,7 +1268,7 @@
         <v>-1588.06</v>
       </c>
       <c r="E10" t="n">
-        <v>688.439072246165</v>
+        <v>711.267896095275</v>
       </c>
     </row>
     <row r="11">
@@ -3592,7 +1285,7 @@
         <v>-845.39</v>
       </c>
       <c r="E11" t="n">
-        <v>694.448589939028</v>
+        <v>720.052775958575</v>
       </c>
     </row>
     <row r="12">
@@ -3609,7 +1302,7 @@
         <v>-2646.36</v>
       </c>
       <c r="E12" t="n">
-        <v>770.223119494327</v>
+        <v>1593.50970817637</v>
       </c>
     </row>
     <row r="13">
@@ -3626,7 +1319,7 @@
         <v>-1385.12</v>
       </c>
       <c r="E13" t="n">
-        <v>-438.531886535665</v>
+        <v>-544.687515795951</v>
       </c>
     </row>
     <row r="14">
@@ -3643,7 +1336,7 @@
         <v>-2594.04</v>
       </c>
       <c r="E14" t="n">
-        <v>648.783809470189</v>
+        <v>903.1536650703</v>
       </c>
     </row>
     <row r="15">
@@ -3660,7 +1353,7 @@
         <v>-1268.92</v>
       </c>
       <c r="E15" t="n">
-        <v>1154.39993221685</v>
+        <v>812.64091515739</v>
       </c>
     </row>
   </sheetData>
@@ -3719,10 +1412,10 @@
         <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.928571428571429</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="4">
@@ -3736,10 +1429,10 @@
         <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.928571428571429</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="5">
@@ -3753,10 +1446,10 @@
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.928571428571429</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="6">
@@ -3770,10 +1463,10 @@
         <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.928571428571429</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="7">
@@ -3787,10 +1480,10 @@
         <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.928571428571429</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="8">
@@ -3804,10 +1497,10 @@
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.928571428571429</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="9">
@@ -3821,10 +1514,10 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.928571428571429</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="10">
@@ -3838,10 +1531,10 @@
         <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0.857142857142857</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="11">
@@ -3855,10 +1548,10 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.857142857142857</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="12">
@@ -3872,10 +1565,10 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
-        <v>0.857142857142857</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="13">
@@ -3889,10 +1582,10 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.857142857142857</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="14">
@@ -3906,10 +1599,10 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="15">
@@ -3923,10 +1616,10 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="16">
@@ -3940,10 +1633,10 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="17">
@@ -3957,10 +1650,10 @@
         <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="18">
@@ -3974,10 +1667,10 @@
         <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="19">
@@ -3991,10 +1684,10 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>0.785714285714286</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="20">
@@ -4008,10 +1701,10 @@
         <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E20" t="n">
-        <v>0.785714285714286</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="21">
@@ -4025,10 +1718,10 @@
         <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
-        <v>0.785714285714286</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="22">
@@ -4042,10 +1735,10 @@
         <v>57</v>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E22" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="23">
@@ -4059,10 +1752,10 @@
         <v>58</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E23" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="24">
@@ -4076,10 +1769,10 @@
         <v>59</v>
       </c>
       <c r="D24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E24" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="25">
@@ -4093,10 +1786,10 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E25" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="26">
@@ -4110,10 +1803,10 @@
         <v>61</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>0.714285714285714</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="27">
@@ -4127,10 +1820,10 @@
         <v>62</v>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>0.714285714285714</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="28">
@@ -4144,10 +1837,10 @@
         <v>63</v>
       </c>
       <c r="D28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="29">
@@ -4161,10 +1854,10 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="30">
@@ -4178,10 +1871,10 @@
         <v>65</v>
       </c>
       <c r="D30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="31">
@@ -4246,10 +1939,10 @@
         <v>69</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35">
@@ -4263,10 +1956,10 @@
         <v>70</v>
       </c>
       <c r="D35" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E35" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
@@ -4280,10 +1973,10 @@
         <v>71</v>
       </c>
       <c r="D36" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E36" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37">
@@ -4314,10 +2007,10 @@
         <v>73</v>
       </c>
       <c r="D38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="39">
@@ -4331,10 +2024,10 @@
         <v>74</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="40">
@@ -4365,10 +2058,10 @@
         <v>76</v>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E41" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="42">
@@ -4382,10 +2075,10 @@
         <v>77</v>
       </c>
       <c r="D42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E42" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="43">
@@ -4399,10 +2092,10 @@
         <v>78</v>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E43" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="44">
@@ -4416,10 +2109,10 @@
         <v>79</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>0.357142857142857</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="45">
@@ -4450,10 +2143,10 @@
         <v>81</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="47">
@@ -4467,10 +2160,10 @@
         <v>82</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="48">
@@ -4484,10 +2177,10 @@
         <v>83</v>
       </c>
       <c r="D48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="49">
@@ -4501,10 +2194,10 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="50">
@@ -4518,10 +2211,10 @@
         <v>85</v>
       </c>
       <c r="D50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="51">
@@ -4535,10 +2228,10 @@
         <v>86</v>
       </c>
       <c r="D51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="52">
@@ -4552,10 +2245,10 @@
         <v>87</v>
       </c>
       <c r="D52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="53">
@@ -4569,10 +2262,10 @@
         <v>88</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="54">
@@ -4586,10 +2279,10 @@
         <v>89</v>
       </c>
       <c r="D54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="55">
@@ -4603,10 +2296,10 @@
         <v>90</v>
       </c>
       <c r="D55" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="56">
@@ -4620,10 +2313,10 @@
         <v>91</v>
       </c>
       <c r="D56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
-        <v>0.285714285714286</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="57">
@@ -4637,10 +2330,10 @@
         <v>92</v>
       </c>
       <c r="D57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="58">
@@ -4654,10 +2347,10 @@
         <v>93</v>
       </c>
       <c r="D58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="59">
@@ -4671,10 +2364,10 @@
         <v>94</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="60">
@@ -4688,10 +2381,10 @@
         <v>95</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="61">
@@ -4705,10 +2398,10 @@
         <v>96</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="62">
@@ -4943,10 +2636,10 @@
         <v>110</v>
       </c>
       <c r="D75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E75" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="76">
@@ -4960,10 +2653,10 @@
         <v>111</v>
       </c>
       <c r="D76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E76" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="77">
@@ -4977,10 +2670,10 @@
         <v>112</v>
       </c>
       <c r="D77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="78">
@@ -4994,10 +2687,10 @@
         <v>113</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="79">
@@ -5011,10 +2704,10 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="80">
@@ -5028,10 +2721,10 @@
         <v>115</v>
       </c>
       <c r="D80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="81">
@@ -5045,10 +2738,10 @@
         <v>116</v>
       </c>
       <c r="D81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E81" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="82">
@@ -5062,10 +2755,10 @@
         <v>117</v>
       </c>
       <c r="D82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="83">
@@ -5079,10 +2772,10 @@
         <v>118</v>
       </c>
       <c r="D83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="84">
@@ -5096,10 +2789,10 @@
         <v>119</v>
       </c>
       <c r="D84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E84" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="85">
@@ -5113,10 +2806,10 @@
         <v>120</v>
       </c>
       <c r="D85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E85" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="86">
@@ -5130,10 +2823,10 @@
         <v>121</v>
       </c>
       <c r="D86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="87">
@@ -6561,567 +4254,6 @@
         <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="s">
-        <v>206</v>
-      </c>
-      <c r="D171" t="n">
-        <v>1</v>
-      </c>
-      <c r="E171" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="s">
-        <v>207</v>
-      </c>
-      <c r="D172" t="n">
-        <v>1</v>
-      </c>
-      <c r="E172" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="s">
-        <v>208</v>
-      </c>
-      <c r="D173" t="n">
-        <v>1</v>
-      </c>
-      <c r="E173" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="s">
-        <v>209</v>
-      </c>
-      <c r="D174" t="n">
-        <v>1</v>
-      </c>
-      <c r="E174" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="s">
-        <v>210</v>
-      </c>
-      <c r="D175" t="n">
-        <v>1</v>
-      </c>
-      <c r="E175" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="s">
-        <v>211</v>
-      </c>
-      <c r="D176" t="n">
-        <v>1</v>
-      </c>
-      <c r="E176" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="s">
-        <v>212</v>
-      </c>
-      <c r="D177" t="n">
-        <v>1</v>
-      </c>
-      <c r="E177" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="s">
-        <v>213</v>
-      </c>
-      <c r="D178" t="n">
-        <v>1</v>
-      </c>
-      <c r="E178" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="s">
-        <v>214</v>
-      </c>
-      <c r="D179" t="n">
-        <v>1</v>
-      </c>
-      <c r="E179" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="s">
-        <v>215</v>
-      </c>
-      <c r="D180" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="s">
-        <v>216</v>
-      </c>
-      <c r="D181" t="n">
-        <v>1</v>
-      </c>
-      <c r="E181" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="s">
-        <v>217</v>
-      </c>
-      <c r="D182" t="n">
-        <v>1</v>
-      </c>
-      <c r="E182" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="s">
-        <v>218</v>
-      </c>
-      <c r="D183" t="n">
-        <v>1</v>
-      </c>
-      <c r="E183" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="s">
-        <v>219</v>
-      </c>
-      <c r="D184" t="n">
-        <v>1</v>
-      </c>
-      <c r="E184" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="s">
-        <v>220</v>
-      </c>
-      <c r="D185" t="n">
-        <v>1</v>
-      </c>
-      <c r="E185" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="s">
-        <v>221</v>
-      </c>
-      <c r="D186" t="n">
-        <v>1</v>
-      </c>
-      <c r="E186" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="s">
-        <v>222</v>
-      </c>
-      <c r="D187" t="n">
-        <v>1</v>
-      </c>
-      <c r="E187" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="s">
-        <v>223</v>
-      </c>
-      <c r="D188" t="n">
-        <v>1</v>
-      </c>
-      <c r="E188" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="s">
-        <v>224</v>
-      </c>
-      <c r="D189" t="n">
-        <v>1</v>
-      </c>
-      <c r="E189" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="s">
-        <v>225</v>
-      </c>
-      <c r="D190" t="n">
-        <v>1</v>
-      </c>
-      <c r="E190" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="s">
-        <v>226</v>
-      </c>
-      <c r="D191" t="n">
-        <v>1</v>
-      </c>
-      <c r="E191" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="s">
-        <v>227</v>
-      </c>
-      <c r="D192" t="n">
-        <v>1</v>
-      </c>
-      <c r="E192" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="s">
-        <v>228</v>
-      </c>
-      <c r="D193" t="n">
-        <v>1</v>
-      </c>
-      <c r="E193" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="s">
-        <v>229</v>
-      </c>
-      <c r="D194" t="n">
-        <v>1</v>
-      </c>
-      <c r="E194" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="s">
-        <v>230</v>
-      </c>
-      <c r="D195" t="n">
-        <v>1</v>
-      </c>
-      <c r="E195" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="s">
-        <v>231</v>
-      </c>
-      <c r="D196" t="n">
-        <v>1</v>
-      </c>
-      <c r="E196" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="s">
-        <v>232</v>
-      </c>
-      <c r="D197" t="n">
-        <v>1</v>
-      </c>
-      <c r="E197" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="s">
-        <v>233</v>
-      </c>
-      <c r="D198" t="n">
-        <v>1</v>
-      </c>
-      <c r="E198" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="s">
-        <v>234</v>
-      </c>
-      <c r="D199" t="n">
-        <v>1</v>
-      </c>
-      <c r="E199" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="s">
-        <v>235</v>
-      </c>
-      <c r="D200" t="n">
-        <v>1</v>
-      </c>
-      <c r="E200" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="s">
-        <v>236</v>
-      </c>
-      <c r="D201" t="n">
-        <v>1</v>
-      </c>
-      <c r="E201" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="s">
-        <v>15</v>
-      </c>
-      <c r="B202" t="s">
-        <v>16</v>
-      </c>
-      <c r="C202" t="s">
-        <v>237</v>
-      </c>
-      <c r="D202" t="n">
-        <v>1</v>
-      </c>
-      <c r="E202" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="s">
-        <v>15</v>
-      </c>
-      <c r="B203" t="s">
-        <v>16</v>
-      </c>
-      <c r="C203" t="s">
-        <v>238</v>
-      </c>
-      <c r="D203" t="n">
-        <v>1</v>
-      </c>
-      <c r="E203" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/training/d_fcsa_I/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/training/d_fcsa_I/spls/c_data/results.xlsx
@@ -1055,7 +1055,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-1.96453122277527</v>
@@ -1063,10 +1063,18 @@
       <c r="I3" t="n">
         <v>-0.846153846153846</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.935323383084577</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.995024875621891</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.662117980795524</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.709459723844184</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1090,6 +1098,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-2.40636991574647</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.00107320612735</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-2.6421027291018</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.07068987362543</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.281311544310863</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.269779715826017</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.394839008914422</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-2.53343074379818</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.493924126522769</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.19456244350857</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.0311197495346922</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.301607791645982</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.62594817105747</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.487898331650314</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.0497941898538199</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.836089459943196</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.63941315852666</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-1.7346404681002</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.36881756154278</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.15494005962602</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-2.02448190689071</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.07958227428782</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1.39261863226338</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.144677920826891</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.139674816442912</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.902452537752395</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.0860427816770815</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.344036598724444</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-1.28927360187133</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.73951250065303</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.577290256609306</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.155913324590861</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.0442562668105326</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.593506421297795</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.587445795622316</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.52425238768566</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-1.05358246020819</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.442684842293121</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.306369524731517</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.312417370791575</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.904105532980386</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1.22334567474143</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.900317634624726</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.141217882716058</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.0389947408200959</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.676714834501656</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.0262080121974197</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.312732817683507</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.56449664283591</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.689676460929439</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.184482444787541</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-1.98951475636982</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-1.49630415767528</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.503131973131279</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.568957726912993</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.861189855958677</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.345055643527707</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-1.29441678545721</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.784804526313084</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0.0364854643252762</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.941284600059004</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.191500836794072</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.420284454311007</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0.105848569714623</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.259687428053091</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.581272986887722</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.640183084716694</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-1.44848578720362</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1.02881586958388</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-0.586589586069132</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.690067962742291</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1.38159975095437</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-1.87322578557214</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-2.4090819760713</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-0.91093983099531</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.43203697218787</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.612428456227089</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.11367747071056</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.05002221028914</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0.584381878220714</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-1.32370959134144</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.0260270564324887</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.764481114871231</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-2.00785187278158</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.942562460430588</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.520567172678189</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-2.37666371349816</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0.0393912484851744</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.565496987763364</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-2.93853943308334</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.314019740278543</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-1.51153570581738</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-0.210634691708549</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.144675643426989</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-1.52404634526323</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.503846901207496</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.459591097024386</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.61928765319972</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-0.428620292835714</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.309943236232158</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.856132642634253</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-2.68533350087882</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-1.5139036019089</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.397462883303259</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.869929694357901</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.720065595873842</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-1.66226000367852</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.220068147874909</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.250705564362278</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.907668115367682</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.055614836063314</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.0828735526706263</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.526777199186982</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.0294480425246618</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-1.56888904897779</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.608118175900982</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.715545486565707</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-2.24037878623641</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.17628653808011</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.661443124657844</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.394863821365601</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-1.41707327030872</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.316307077025448</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.321825943223849</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.515380312754952</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.136006071938092</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.373526725899013</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-1.65299341751423</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.709428099617677</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1.31379266548537</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.313593413916455</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.280672574953204</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.675579406479978</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-0.204179054462888</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.442204297658344</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.170088036363069</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-0.4732757830384</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.661083022320496</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.121341191303152</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.103794849360212</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.0387696800125888</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.185300457527681</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-1.25396019645081</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.635522536745122</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.111635433750441</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.484910594175294</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.444383439142328</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.228253864956345</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.236906399316726</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.33970271587927</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-0.169347988791324</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.061169052530105</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-1.32312114122161</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.237811388361279</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.01740384866511</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-1.14149506138627</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.425187180998374</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.86910036701696</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-2.04617337540624</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.601495459981501</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-1.07751005433536</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-0.356317217988763</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.508184125564882</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.169239577879509</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-1.56622271008483</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.71581133465104</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.208025596473572</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-1.15003217382327</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.640248355686595</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.086755171398478</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.0804630093712025</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.0909323247784004</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.647567106556637</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>-0.221866874307939</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.188605268325927</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.210804947821043</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.405226670223261</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.327250565270186</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.0186990660129365</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.301176598102252</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.330541062347714</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-0.335022042302735</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-2.34538930560108</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.0618388297677102</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-1.04150672572174</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.888807904704088</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.643847212492755</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.172837007636779</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.482759747550092</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-0.817357552614586</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.173527815119121</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.953552847541445</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-1.34287820741534</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.894473857928341</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.495844673422448</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.439168520474182</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.945556040882629</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-1.70295911312921</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-1.25853628168135</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-0.74304081182949</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
